--- a/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0002T0006Z000C1N9_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0002T0006Z000C1N9_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>35.04478401763448</v>
+        <v>5.694777402865602</v>
       </c>
       <c r="D2" t="n">
-        <v>35.19014589092729</v>
+        <v>5.718398707275685</v>
       </c>
       <c r="E2" t="n">
-        <v>6.641737188201668</v>
+        <v>1.079282293082771</v>
       </c>
       <c r="F2" t="n">
-        <v>7.183445787024097</v>
+        <v>1.167309940391416</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>30.98947814410698</v>
+        <v>5.035790198417384</v>
       </c>
       <c r="D3" t="n">
-        <v>30.84038841483239</v>
+        <v>5.011563117410263</v>
       </c>
       <c r="E3" t="n">
-        <v>6.641737188201668</v>
+        <v>1.079282293082771</v>
       </c>
       <c r="F3" t="n">
-        <v>7.183445787024097</v>
+        <v>1.167309940391416</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>19.37261208417339</v>
+        <v>3.148049463678176</v>
       </c>
       <c r="D4" t="n">
-        <v>18.24982684070555</v>
+        <v>2.965596861614652</v>
       </c>
       <c r="E4" t="n">
-        <v>6.641737188201668</v>
+        <v>1.079282293082771</v>
       </c>
       <c r="F4" t="n">
-        <v>7.183445787024097</v>
+        <v>1.167309940391416</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
